--- a/miltenyi-pms-dev/docs/meetings/notifications-decision-matrix.xlsx
+++ b/miltenyi-pms-dev/docs/meetings/notifications-decision-matrix.xlsx
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>When a submitted review is edited afterwards (mentor or HR), should the employee be told?</t>
+          <t>Can a submitted review be edited afterwards, and should the staff member be told?</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Bell + email to the staff member: 'Your Q3 · CY 2026 project goals review was edited by &lt;Mentor&gt;.' Only for a quarter that is still open (current or backfill).</t>
+          <t>Not possible any more (UAT feedback 11 Sep 2026): a submitted quarterly review is final for the mentor and the Admin. The correction path is the Admin unlock (6.6), after which the mentor resubmits and the staff member gets the 'review is in' message again (6.4). No 'review edited' notification exists.</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Keep the bell. Email optional. The change log is the audit trail; HR can open it from the set page.</t>
+          <t>Keep it this way: one submission per quarter, corrections only through an Admin unlock with a reason.</t>
         </is>
       </c>
       <c r="E6" s="3" t="n"/>
